--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
   <si>
     <t>Filename</t>
   </si>
@@ -811,661 +811,667 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9780,0.0041,0.0058,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.2788,0.0001,0.0007,0.8360</t>
-  </si>
-  <si>
-    <t>0.0381,0.0001,0.0006,0.9863</t>
+    <t>0.8959,0.0144,0.0279,0.0051</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9517,0.0004,0.0003,0.0444</t>
+  </si>
+  <si>
+    <t>0.0099,0.0000,0.0001,0.9973</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0029,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8749,0.0030,0.0614,0.0023</t>
+  </si>
+  <si>
+    <t>0.0351,0.0010,0.9734,0.0002</t>
+  </si>
+  <si>
+    <t>0.5121,0.0012,0.6173,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.0005,0.9927,0.0002</t>
+  </si>
+  <si>
+    <t>0.9212,0.0001,0.0850,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0185,0.9816,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8316,0.0002,0.1497,0.0015</t>
+  </si>
+  <si>
+    <t>0.6234,0.0006,0.2726,0.0027</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.0425,0.0000,0.9846,0.0000</t>
+  </si>
+  <si>
+    <t>0.0065,0.0005,0.9888,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0351,0.9648,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9683,0.0226,0.0072,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0007,0.9994,0.0015</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0006,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9121,0.0006,0.1001,0.0003</t>
+  </si>
+  <si>
+    <t>0.3160,0.7420,0.0017,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9992,0.0066,0.0000</t>
+  </si>
+  <si>
+    <t>0.0062,0.9354,0.0412,0.0015</t>
+  </si>
+  <si>
+    <t>0.0146,0.0005,0.9758,0.0012</t>
+  </si>
+  <si>
+    <t>0.0015,0.0015,0.9942,0.0007</t>
+  </si>
+  <si>
+    <t>0.0057,0.0000,0.9625,0.0017</t>
+  </si>
+  <si>
+    <t>0.0009,0.0008,0.9985,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0011,0.9947,0.0182</t>
+  </si>
+  <si>
+    <t>0.0009,0.5586,0.0001,0.9801</t>
+  </si>
+  <si>
+    <t>0.0026,0.9917,0.0000,0.0007</t>
+  </si>
+  <si>
+    <t>0.0007,0.9983,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0022,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0006,0.9986,0.0016</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0008,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,1.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.7411,0.9936,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0011,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9982,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0004</t>
+  </si>
+  <si>
+    <t>0.0016,0.9983,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8342,0.0002,0.2554,0.0001</t>
+  </si>
+  <si>
+    <t>0.8835,0.0035,0.0686,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0025,0.9997,0.0011</t>
+  </si>
+  <si>
+    <t>0.0000,0.9978,0.9970,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.8951,0.9485,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.2896,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9044,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0016,0.9996</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0055,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0167,0.9997</t>
+  </si>
+  <si>
+    <t>0.0001,0.0024,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9625,0.9811,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9961,0.9885,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.7587,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9912,0.2918,0.0000</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
+    <t>0.9991,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0024,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0007,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9997,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0008,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.5685,0.0112,0.2567,0.0013</t>
-  </si>
-  <si>
-    <t>0.0007,0.0064,0.9975,0.0003</t>
-  </si>
-  <si>
-    <t>0.0371,0.0025,0.9705,0.0001</t>
-  </si>
-  <si>
-    <t>0.5462,0.0002,0.5873,0.0001</t>
-  </si>
-  <si>
-    <t>0.8785,0.0012,0.0763,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9988,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0162,0.9844,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9990,0.0001,0.0007</t>
+    <t>0.9958,0.0053,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0005,0.9981,0.0004</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.7303,0.0108,0.0265,0.0393</t>
+  </si>
+  <si>
+    <t>0.0078,0.0004,0.9912,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.2417,0.0004,0.5482,0.0220</t>
-  </si>
-  <si>
-    <t>0.3653,0.0008,0.6784,0.0004</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0134,0.0010,0.9821,0.0004</t>
-  </si>
-  <si>
-    <t>0.0621,0.0000,0.9772,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0042,0.0000,0.9976,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.9929,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9503,0.0193,0.0179,0.0005</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9996,0.0008</t>
-  </si>
-  <si>
-    <t>0.0002,0.9993,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0494,0.9501,0.0020,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9927,0.1254,0.0001</t>
-  </si>
-  <si>
-    <t>0.0049,0.9707,0.0383,0.0011</t>
-  </si>
-  <si>
-    <t>0.0004,0.0004,0.9987,0.0002</t>
-  </si>
-  <si>
-    <t>0.0078,0.0013,0.9823,0.0007</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0012,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9985,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0011,0.9972,0.0021</t>
-  </si>
-  <si>
-    <t>0.1341,0.0174,0.0001,0.7938</t>
-  </si>
-  <si>
-    <t>0.0007,0.9975,0.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.9987,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0018,0.0005,0.9944,0.0035</t>
-  </si>
-  <si>
-    <t>0.0094,0.0003,0.9937,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0003,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9817,0.0082,0.0071,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.0029,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0018,0.0000,0.0000</t>
+    <t>0.0003,0.9990,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9977,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.1665,0.8938,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.8994,0.0081,0.0494,0.0021</t>
+  </si>
+  <si>
+    <t>0.0654,0.0001,0.9644,0.0001</t>
+  </si>
+  <si>
+    <t>0.9493,0.0040,0.0130,0.0021</t>
+  </si>
+  <si>
+    <t>0.0066,0.0102,0.9808,0.0036</t>
+  </si>
+  <si>
+    <t>0.0005,0.5867,0.0021,0.9573</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9954,0.9807,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9753,0.0254,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9531,0.0308,0.0109,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9983,0.0000,0.0000,0.0016</t>
+  </si>
+  <si>
+    <t>0.9987,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.5610,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9295,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0106,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.9971,0.0003</t>
+  </si>
+  <si>
+    <t>0.9991,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.8241,0.0102,0.0845,0.0028</t>
+  </si>
+  <si>
+    <t>0.5505,0.0001,0.4516,0.0006</t>
+  </si>
+  <si>
+    <t>0.9114,0.0009,0.0584,0.0032</t>
+  </si>
+  <si>
+    <t>0.0289,0.0000,0.0000,0.9949</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0009,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9966,0.9183,0.0000</t>
+  </si>
+  <si>
+    <t>0.0655,0.9348,0.0014,0.0011</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9255,0.9977,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0022,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.9956,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0037,0.9965,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0003,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.9732,0.0015,0.0176,0.0002</t>
-  </si>
-  <si>
-    <t>0.0008,0.0036,0.9989,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9948,0.9946,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9955,0.9694,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.6561,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9732,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.0060,0.9988</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.0044,0.9989</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0003,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9509,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9930,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9778,0.9899,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9945,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.8815,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0152,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0029,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0059,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9975,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0002,0.9983,0.0002</t>
-  </si>
-  <si>
-    <t>0.0035,0.0006,0.9958,0.0001</t>
-  </si>
-  <si>
-    <t>0.9608,0.0001,0.0244,0.0012</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9980,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.9993,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9992,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9985,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.2711,0.8281,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.6210,0.0032,0.3474,0.0013</t>
-  </si>
-  <si>
-    <t>0.6736,0.0001,0.3748,0.0003</t>
-  </si>
-  <si>
-    <t>0.8321,0.0009,0.1431,0.0014</t>
-  </si>
-  <si>
-    <t>0.9228,0.0030,0.0406,0.0020</t>
-  </si>
-  <si>
-    <t>0.0015,0.8101,0.0031,0.8134</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9881,0.9165,0.0001</t>
-  </si>
-  <si>
-    <t>0.5986,0.5200,0.0009,0.0000</t>
-  </si>
-  <si>
-    <t>0.9047,0.1267,0.0008,0.0001</t>
+    <t>0.0052,0.9959,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.4186,0.0000,0.0008,0.7128</t>
+  </si>
+  <si>
+    <t>0.0006,0.0013,0.9960,0.0218</t>
+  </si>
+  <si>
+    <t>0.9983,0.0000,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9982,0.0000,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.1152,0.9214,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0004,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9813,0.0077,0.0028,0.0003</t>
+  </si>
+  <si>
+    <t>0.7827,0.0683,0.0143,0.0028</t>
+  </si>
+  <si>
+    <t>0.4918,0.0077,0.4469,0.0004</t>
+  </si>
+  <si>
+    <t>0.9896,0.0038,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0005,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9993,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.4898,0.9969,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.6512,0.9976,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0009,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9040,0.0061,0.0322,0.0052</t>
-  </si>
-  <si>
-    <t>0.7166,0.0000,0.3233,0.0003</t>
-  </si>
-  <si>
-    <t>0.9778,0.0013,0.0066,0.0005</t>
-  </si>
-  <si>
-    <t>0.0051,0.0001,0.0002,0.9982</t>
-  </si>
-  <si>
-    <t>0.0001,0.9946,0.5934,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0079,0.9835,0.0032,0.0062</t>
-  </si>
-  <si>
-    <t>0.0382,0.9725,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2324,0.0001,0.0009,0.8611</t>
-  </si>
-  <si>
-    <t>0.0005,0.0007,0.9987,0.0009</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0000,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0152,0.9862,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9856,0.0044,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.5340,0.0541,0.1083,0.0024</t>
-  </si>
-  <si>
-    <t>0.2379,0.0023,0.7851,0.0004</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0012,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9174,0.1157,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9737,0.0316,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9690,0.0024,0.0148,0.0012</t>
-  </si>
-  <si>
-    <t>0.9869,0.0179,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0004,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9648,0.0057,0.0198,0.0005</t>
-  </si>
-  <si>
-    <t>0.0008,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9902,0.0080,0.0019,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0026,0.0014,0.9948,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0025,0.0389,0.9870,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0905,0.0064,0.8782,0.0016</t>
-  </si>
-  <si>
-    <t>0.0664,0.0020,0.9483,0.0003</t>
-  </si>
-  <si>
-    <t>0.7492,0.0013,0.2288,0.0022</t>
-  </si>
-  <si>
-    <t>0.1395,0.0094,0.8419,0.0003</t>
-  </si>
-  <si>
-    <t>0.0372,0.2532,0.4779,0.0003</t>
-  </si>
-  <si>
-    <t>0.9532,0.0037,0.0375,0.0001</t>
-  </si>
-  <si>
-    <t>0.9719,0.0012,0.0098,0.0014</t>
-  </si>
-  <si>
-    <t>0.6836,0.0021,0.3613,0.0005</t>
-  </si>
-  <si>
-    <t>0.0273,0.9781,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9988,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9405,0.0998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8751,0.2160,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0147,0.9851,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9907,0.0004,0.0023,0.0001</t>
-  </si>
-  <si>
-    <t>0.7805,0.0019,0.1852,0.0022</t>
-  </si>
-  <si>
-    <t>0.9169,0.0094,0.0012,0.0080</t>
-  </si>
-  <si>
-    <t>0.9702,0.0037,0.0068,0.0008</t>
-  </si>
-  <si>
-    <t>0.9354,0.0004,0.0757,0.0004</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.9983,0.0004</t>
-  </si>
-  <si>
-    <t>0.0179,0.0007,0.9706,0.0015</t>
-  </si>
-  <si>
-    <t>0.0132,0.0405,0.9601,0.0015</t>
-  </si>
-  <si>
-    <t>0.0312,0.0007,0.9693,0.0003</t>
-  </si>
-  <si>
-    <t>0.0023,0.0944,0.9644,0.0004</t>
-  </si>
-  <si>
-    <t>0.9918,0.0090,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9758,0.0191,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.9986,0.0010,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9987,0.0010,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.0305,0.1238,0.7902,0.0009</t>
-  </si>
-  <si>
-    <t>0.9967,0.0002,0.0008,0.0006</t>
-  </si>
-  <si>
-    <t>0.0047,0.0001,0.9983,0.0000</t>
+    <t>0.9940,0.0038,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.3370,0.7726,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.9794,0.0245,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0945,0.0003,0.9406,0.0005</t>
+  </si>
+  <si>
+    <t>0.8041,0.3095,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0003,0.0007</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9575,0.0169,0.0167,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9913,0.0025,0.0033,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0022,0.0205,0.9866,0.0026</t>
   </si>
   <si>
     <t>0.0003,0.0006,0.9995,0.0000</t>
   </si>
   <si>
-    <t>0.0024,0.7118,0.7764,0.0001</t>
-  </si>
-  <si>
-    <t>0.0030,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.6505,0.0006,0.4016,0.0011</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.0010,0.0045,0.9964,0.0013</t>
-  </si>
-  <si>
-    <t>0.9852,0.0002,0.0065,0.0007</t>
-  </si>
-  <si>
-    <t>0.9831,0.0002,0.0103,0.0004</t>
-  </si>
-  <si>
-    <t>0.9984,0.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0028,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0018,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9984,0.0009,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0064,0.0130,0.9795,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0188,0.9963,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0009,0.9961,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0140,0.0001,0.9391,0.0034</t>
-  </si>
-  <si>
-    <t>0.2205,0.0005,0.8132,0.0006</t>
-  </si>
-  <si>
-    <t>0.0022,0.0009,0.9919,0.0033</t>
-  </si>
-  <si>
-    <t>0.9701,0.0000,0.0001,0.0453</t>
-  </si>
-  <si>
-    <t>0.0037,0.0014,0.0000,0.9985</t>
-  </si>
-  <si>
-    <t>0.0117,0.0000,0.0000,0.9981</t>
-  </si>
-  <si>
-    <t>0.9986,0.0001,0.0000,0.0001</t>
+    <t>0.0002,0.0289,0.9988,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0781,0.0002,0.9312,0.0004</t>
+  </si>
+  <si>
+    <t>0.1636,0.0006,0.8886,0.0003</t>
+  </si>
+  <si>
+    <t>0.0025,0.0026,0.9936,0.0003</t>
+  </si>
+  <si>
+    <t>0.7397,0.0698,0.0663,0.0004</t>
+  </si>
+  <si>
+    <t>0.2400,0.1319,0.2488,0.0006</t>
+  </si>
+  <si>
+    <t>0.7962,0.0082,0.1984,0.0006</t>
+  </si>
+  <si>
+    <t>0.9673,0.0015,0.0144,0.0009</t>
+  </si>
+  <si>
+    <t>0.1710,0.0079,0.7877,0.0020</t>
+  </si>
+  <si>
+    <t>0.0060,0.9933,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9991,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9532,0.0871,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5763,0.5472,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0125,0.9884,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9812,0.0029,0.0043,0.0001</t>
+  </si>
+  <si>
+    <t>0.9469,0.0004,0.0455,0.0008</t>
+  </si>
+  <si>
+    <t>0.9928,0.0001,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.7147,0.0484,0.0909,0.0087</t>
+  </si>
+  <si>
+    <t>0.8965,0.0002,0.1140,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.0013,0.0009,0.9927,0.0024</t>
+  </si>
+  <si>
+    <t>0.0021,0.0119,0.9878,0.0015</t>
+  </si>
+  <si>
+    <t>0.0041,0.0003,0.9957,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0032,0.9914,0.0006</t>
+  </si>
+  <si>
+    <t>0.9987,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9934,0.0031,0.0008,0.0009</t>
+  </si>
+  <si>
+    <t>0.9991,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0468,0.2061,0.7482,0.0011</t>
+  </si>
+  <si>
+    <t>0.9843,0.0008,0.0067,0.0010</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0010,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.0554,0.9924,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0222,0.0008,0.9745,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0008,0.9940,0.0022</t>
+  </si>
+  <si>
+    <t>0.0007,0.0154,0.9968,0.0006</t>
+  </si>
+  <si>
+    <t>0.9579,0.0010,0.0253,0.0010</t>
+  </si>
+  <si>
+    <t>0.9429,0.0003,0.0411,0.0012</t>
+  </si>
+  <si>
+    <t>0.9955,0.0003,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9896,0.0158,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9927,0.0076,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0331,0.0213,0.8907,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9991,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.7036,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0140,0.0148,0.9378,0.0017</t>
+  </si>
+  <si>
+    <t>0.0102,0.0001,0.9932,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.9519,0.0437</t>
+  </si>
+  <si>
+    <t>0.1965,0.0003,0.8112,0.0008</t>
+  </si>
+  <si>
+    <t>0.0178,0.0005,0.9731,0.0034</t>
+  </si>
+  <si>
+    <t>0.9743,0.0000,0.0005,0.0206</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0242,0.0000,0.0000,0.9975</t>
+  </si>
+  <si>
+    <t>0.9946,0.0003,0.0001,0.0008</t>
   </si>
 </sst>
 </file>
@@ -1876,7 +1882,7 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
         <v>267</v>
@@ -1935,7 +1941,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1949,7 +1955,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1963,7 +1969,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1977,7 +1983,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1991,7 +1997,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2005,7 +2011,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2019,7 +2025,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2033,7 +2039,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2047,7 +2053,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2061,7 +2067,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2075,7 +2081,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2089,7 +2095,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2103,7 +2109,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2117,7 +2123,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2131,7 +2137,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2145,7 +2151,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2156,10 +2162,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2170,10 +2176,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2187,7 +2193,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2201,7 +2207,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2215,7 +2221,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2229,7 +2235,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2243,7 +2249,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2257,7 +2263,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2271,7 +2277,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2285,7 +2291,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2299,7 +2305,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2313,7 +2319,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2327,7 +2333,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2341,7 +2347,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2355,7 +2361,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2369,7 +2375,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2383,7 +2389,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2397,7 +2403,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2411,7 +2417,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2425,7 +2431,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2439,7 +2445,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2453,7 +2459,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2464,10 +2470,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2481,7 +2487,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2495,7 +2501,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2509,7 +2515,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2607,7 +2613,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>271</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2621,7 +2627,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2635,7 +2641,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2649,7 +2655,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2663,7 +2669,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2870,7 +2876,7 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
         <v>333</v>
@@ -3083,7 +3089,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3097,7 +3103,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>347</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3111,7 +3117,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3125,7 +3131,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3139,7 +3145,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3153,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3167,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3181,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3195,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>353</v>
+        <v>270</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3209,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3223,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3237,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3251,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3265,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3279,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3293,7 +3299,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3307,7 +3313,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3321,7 +3327,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3335,7 +3341,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3349,7 +3355,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3363,7 +3369,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3377,7 +3383,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3391,7 +3397,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3405,7 +3411,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>361</v>
+        <v>278</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3419,7 +3425,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>283</v>
+        <v>363</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3458,7 +3464,7 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
         <v>366</v>
@@ -3486,7 +3492,7 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
         <v>368</v>
@@ -3531,7 +3537,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3545,7 +3551,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>279</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3573,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3584,10 +3590,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3601,7 +3607,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3615,7 +3621,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>270</v>
+        <v>352</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3629,7 +3635,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>269</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3643,7 +3649,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3657,7 +3663,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>320</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3671,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>269</v>
+        <v>347</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3685,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3699,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3713,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3724,10 +3730,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3741,7 +3747,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3755,7 +3761,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3769,7 +3775,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3783,7 +3789,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3797,7 +3803,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3811,7 +3817,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3825,7 +3831,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3839,7 +3845,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3853,7 +3859,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3867,7 +3873,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>336</v>
+        <v>391</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3881,7 +3887,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>336</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3895,7 +3901,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3909,7 +3915,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>389</v>
+        <v>352</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3923,7 +3929,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3937,7 +3943,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3951,7 +3957,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3965,7 +3971,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3979,7 +3985,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3993,7 +3999,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4007,7 +4013,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4021,7 +4027,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4035,7 +4041,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4049,7 +4055,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4063,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4077,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4091,7 +4097,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4102,10 +4108,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4119,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4133,7 +4139,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4147,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>352</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4161,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4175,7 +4181,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4189,7 +4195,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>320</v>
+        <v>395</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4203,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4217,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4231,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4245,7 +4251,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4256,10 +4262,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4273,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4284,10 +4290,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4301,7 +4307,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4315,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4329,7 +4335,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4343,7 +4349,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4357,7 +4363,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4371,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4385,7 +4391,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4399,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4413,7 +4419,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4427,7 +4433,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4441,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4455,7 +4461,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4469,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4483,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4497,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4508,10 +4514,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4522,10 +4528,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4539,7 +4545,7 @@
         <v>259</v>
       </c>
       <c r="D194" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4553,7 +4559,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4567,7 +4573,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4578,10 +4584,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4595,7 +4601,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4609,7 +4615,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4623,7 +4629,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4634,10 +4640,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4651,7 +4657,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4665,7 +4671,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4679,7 +4685,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4693,7 +4699,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4707,7 +4713,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4721,7 +4727,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4735,7 +4741,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4749,7 +4755,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4763,7 +4769,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4777,7 +4783,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4791,7 +4797,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4805,7 +4811,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>271</v>
+        <v>347</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4819,7 +4825,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4833,7 +4839,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4847,7 +4853,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>270</v>
+        <v>455</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4861,7 +4867,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>451</v>
+        <v>352</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4875,7 +4881,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>452</v>
+        <v>320</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4889,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4903,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>270</v>
+        <v>412</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4917,7 +4923,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>454</v>
+        <v>325</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4931,7 +4937,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4945,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4959,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4973,7 +4979,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4984,10 +4990,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5001,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5012,10 +5018,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5029,7 +5035,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5043,7 +5049,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5057,7 +5063,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5071,7 +5077,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5085,7 +5091,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5099,7 +5105,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5113,7 +5119,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>270</v>
+        <v>470</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5127,7 +5133,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5141,7 +5147,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5155,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5169,7 +5175,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>269</v>
+        <v>411</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5183,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>470</v>
+        <v>320</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5197,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5211,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>348</v>
+        <v>473</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5225,7 +5231,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5239,7 +5245,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5250,10 +5256,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D245" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5267,7 +5273,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5281,7 +5287,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5295,7 +5301,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5309,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5323,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5337,7 +5343,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5351,7 +5357,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5365,7 +5371,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5379,7 +5385,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5393,7 +5399,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>336</v>
+        <v>390</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5407,7 +5413,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="492">
   <si>
     <t>Filename</t>
   </si>
@@ -811,667 +811,685 @@
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8959,0.0144,0.0279,0.0051</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.9517,0.0004,0.0003,0.0444</t>
-  </si>
-  <si>
-    <t>0.0099,0.0000,0.0001,0.9973</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9415,0.0212,0.0063,0.0016</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.9698,0.0001,0.0000,0.0442</t>
+  </si>
+  <si>
+    <t>0.0040,0.0000,0.0002,0.9985</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9967,0.0029,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8749,0.0030,0.0614,0.0023</t>
-  </si>
-  <si>
-    <t>0.0351,0.0010,0.9734,0.0002</t>
-  </si>
-  <si>
-    <t>0.5121,0.0012,0.6173,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0005,0.9927,0.0002</t>
-  </si>
-  <si>
-    <t>0.9212,0.0001,0.0850,0.0005</t>
+    <t>0.7885,0.0010,0.1414,0.0012</t>
+  </si>
+  <si>
+    <t>0.3571,0.0006,0.7462,0.0002</t>
+  </si>
+  <si>
+    <t>0.0538,0.0090,0.9276,0.0003</t>
+  </si>
+  <si>
+    <t>0.3743,0.0002,0.7181,0.0002</t>
+  </si>
+  <si>
+    <t>0.9956,0.0006,0.0012,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9993,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0185,0.9816,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8316,0.0002,0.1497,0.0015</t>
-  </si>
-  <si>
-    <t>0.6234,0.0006,0.2726,0.0027</t>
+    <t>0.0002,0.9996,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0277,0.9733,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9737,0.0003,0.0133,0.0008</t>
+  </si>
+  <si>
+    <t>0.4051,0.0002,0.6092,0.0007</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0057,0.0011,0.9870,0.0007</t>
+  </si>
+  <si>
+    <t>0.0080,0.0000,0.9959,0.0000</t>
+  </si>
+  <si>
+    <t>0.0399,0.0001,0.9639,0.0003</t>
+  </si>
+  <si>
+    <t>0.0744,0.0000,0.9577,0.0003</t>
+  </si>
+  <si>
+    <t>0.1535,0.8770,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9641,0.0198,0.0076,0.0005</t>
+  </si>
+  <si>
+    <t>0.0006,0.0007,0.9993,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9925,0.0047,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0002,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.1996,0.8551,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9983,0.0022,0.0000</t>
+  </si>
+  <si>
+    <t>0.0027,0.9896,0.0061,0.0017</t>
+  </si>
+  <si>
+    <t>0.0068,0.0025,0.9874,0.0006</t>
+  </si>
+  <si>
+    <t>0.0011,0.0170,0.9940,0.0005</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9978,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9991,0.0035</t>
+  </si>
+  <si>
+    <t>0.0041,0.5045,0.0003,0.9561</t>
+  </si>
+  <si>
+    <t>0.0010,0.9949,0.0000,0.0010</t>
+  </si>
+  <si>
+    <t>0.0005,0.9986,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0048,0.0003,0.9917,0.0009</t>
+  </si>
+  <si>
+    <t>0.0166,0.0000,0.9910,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9991,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0002,0.0060,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0009,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9892,0.0125,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9881,0.8865,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0003,0.9984,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9958,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0003,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.1172,0.0002,0.9367,0.0001</t>
+  </si>
+  <si>
+    <t>0.0008,0.0013,0.9991,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9745,0.9924,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9216,0.9662,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.9124,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9946,0.9518,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0018,0.9991</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0009,0.9999</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.0031,0.9992</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9957,0.9886,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9953,0.9954,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9819,0.9695,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9935,0.9947,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9480,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9991,0.8208,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0014,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0085,0.0004,0.9901,0.0004</t>
+  </si>
+  <si>
+    <t>0.9943,0.0002,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0016,0.0001,0.9983,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.9953,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.9988,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.5897,0.5085,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.4772,0.0030,0.4940,0.0013</t>
+  </si>
+  <si>
+    <t>0.9447,0.0003,0.0596,0.0002</t>
+  </si>
+  <si>
+    <t>0.9638,0.0029,0.0093,0.0008</t>
+  </si>
+  <si>
+    <t>0.9515,0.0040,0.0242,0.0007</t>
+  </si>
+  <si>
+    <t>0.0064,0.5859,0.0008,0.8280</t>
+  </si>
+  <si>
+    <t>0.0006,0.9985,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9427,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9419,0.0741,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9682,0.0340,0.0011,0.0003</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0031,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.4637,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7676,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0028,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0009,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0410,0.0023,0.9431,0.0012</t>
+  </si>
+  <si>
+    <t>0.1440,0.0000,0.9061,0.0002</t>
+  </si>
+  <si>
+    <t>0.8145,0.0126,0.0612,0.0145</t>
+  </si>
+  <si>
+    <t>0.0036,0.0000,0.0000,0.9994</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0001,0.9886,0.8118,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.1425,0.8529,0.0009,0.0014</t>
+  </si>
+  <si>
+    <t>0.2896,0.8467,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.2130,0.0000,0.0359,0.5931</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0019,0.9971,0.0028</t>
+  </si>
+  <si>
+    <t>0.9986,0.0000,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9971,0.0000,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.1204,0.9095,0.0014,0.0000</t>
+  </si>
+  <si>
+    <t>0.9982,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9922,0.0013,0.0023,0.0001</t>
+  </si>
+  <si>
+    <t>0.2479,0.0507,0.2573,0.0030</t>
+  </si>
+  <si>
+    <t>0.6897,0.0902,0.0969,0.0009</t>
+  </si>
+  <si>
+    <t>0.9977,0.0003,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9968,0.0006,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9879,0.0086,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9620,0.0554,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9399,0.0671,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9896,0.0026,0.0038,0.0002</t>
+  </si>
+  <si>
+    <t>0.9940,0.0060,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9986,0.0004,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9985,0.0006,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9799,0.0052,0.0093,0.0004</t>
+  </si>
+  <si>
+    <t>0.0014,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.9912,0.0088,0.0010,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0015,0.9990,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0132,0.9971,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0019,0.9999,0.0000</t>
   </si>
   <si>
     <t>0.0001,0.0000,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0006,0.0002,0.9984,0.0003</t>
-  </si>
-  <si>
-    <t>0.0425,0.0000,0.9846,0.0000</t>
-  </si>
-  <si>
-    <t>0.0065,0.0005,0.9888,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0000,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0351,0.9648,0.0024,0.0001</t>
-  </si>
-  <si>
-    <t>0.9683,0.0226,0.0072,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.0007,0.9994,0.0015</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9121,0.0006,0.1001,0.0003</t>
-  </si>
-  <si>
-    <t>0.3160,0.7420,0.0017,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9992,0.0066,0.0000</t>
-  </si>
-  <si>
-    <t>0.0062,0.9354,0.0412,0.0015</t>
-  </si>
-  <si>
-    <t>0.0146,0.0005,0.9758,0.0012</t>
-  </si>
-  <si>
-    <t>0.0015,0.0015,0.9942,0.0007</t>
-  </si>
-  <si>
-    <t>0.0057,0.0000,0.9625,0.0017</t>
-  </si>
-  <si>
-    <t>0.0009,0.0008,0.9985,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0011,0.9947,0.0182</t>
-  </si>
-  <si>
-    <t>0.0009,0.5586,0.0001,0.9801</t>
-  </si>
-  <si>
-    <t>0.0026,0.9917,0.0000,0.0007</t>
-  </si>
-  <si>
-    <t>0.0007,0.9983,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0022,0.9994,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9986,0.0016</t>
-  </si>
-  <si>
-    <t>0.0023,0.0000,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.7411,0.9936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0011,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9982,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0004</t>
-  </si>
-  <si>
-    <t>0.0016,0.9983,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.8342,0.0002,0.2554,0.0001</t>
-  </si>
-  <si>
-    <t>0.8835,0.0035,0.0686,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.9997,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9970,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.8951,0.9485,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.2896,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.9044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0016,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.0005,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.0055,0.9995</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0167,0.9997</t>
-  </si>
-  <si>
-    <t>0.0001,0.0024,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9991,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9625,0.9811,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9961,0.9885,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.7587,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9912,0.2918,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9974,0.0024,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9958,0.0053,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0005,0.9981,0.0004</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.7303,0.0108,0.0265,0.0393</t>
-  </si>
-  <si>
-    <t>0.0078,0.0004,0.9912,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9995,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9990,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9977,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.1665,0.8938,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8994,0.0081,0.0494,0.0021</t>
-  </si>
-  <si>
-    <t>0.0654,0.0001,0.9644,0.0001</t>
-  </si>
-  <si>
-    <t>0.9493,0.0040,0.0130,0.0021</t>
-  </si>
-  <si>
-    <t>0.0066,0.0102,0.9808,0.0036</t>
-  </si>
-  <si>
-    <t>0.0005,0.5867,0.0021,0.9573</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.9954,0.9807,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9753,0.0254,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9531,0.0308,0.0109,0.0003</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0000,0.0016</t>
-  </si>
-  <si>
-    <t>0.9987,0.0002,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0003,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.5610,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9295,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0106,0.9981,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0006,0.9971,0.0003</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8241,0.0102,0.0845,0.0028</t>
-  </si>
-  <si>
-    <t>0.5505,0.0001,0.4516,0.0006</t>
-  </si>
-  <si>
-    <t>0.9114,0.0009,0.0584,0.0032</t>
-  </si>
-  <si>
-    <t>0.0289,0.0000,0.0000,0.9949</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0009,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9966,0.9183,0.0000</t>
-  </si>
-  <si>
-    <t>0.0655,0.9348,0.0014,0.0011</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0052,0.9959,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.4186,0.0000,0.0008,0.7128</t>
-  </si>
-  <si>
-    <t>0.0006,0.0013,0.9960,0.0218</t>
-  </si>
-  <si>
-    <t>0.9983,0.0000,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9982,0.0000,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.1152,0.9214,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0004,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9813,0.0077,0.0028,0.0003</t>
-  </si>
-  <si>
-    <t>0.7827,0.0683,0.0143,0.0028</t>
-  </si>
-  <si>
-    <t>0.4918,0.0077,0.4469,0.0004</t>
-  </si>
-  <si>
-    <t>0.9896,0.0038,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0038,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.3370,0.7726,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.9794,0.0245,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0945,0.0003,0.9406,0.0005</t>
-  </si>
-  <si>
-    <t>0.8041,0.3095,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9982,0.0002,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9575,0.0169,0.0167,0.0015</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9913,0.0025,0.0033,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0022,0.0205,0.9866,0.0026</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0289,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0781,0.0002,0.9312,0.0004</t>
-  </si>
-  <si>
-    <t>0.1636,0.0006,0.8886,0.0003</t>
-  </si>
-  <si>
-    <t>0.0025,0.0026,0.9936,0.0003</t>
-  </si>
-  <si>
-    <t>0.7397,0.0698,0.0663,0.0004</t>
-  </si>
-  <si>
-    <t>0.2400,0.1319,0.2488,0.0006</t>
-  </si>
-  <si>
-    <t>0.7962,0.0082,0.1984,0.0006</t>
-  </si>
-  <si>
-    <t>0.9673,0.0015,0.0144,0.0009</t>
-  </si>
-  <si>
-    <t>0.1710,0.0079,0.7877,0.0020</t>
-  </si>
-  <si>
-    <t>0.0060,0.9933,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9991,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9532,0.0871,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.5763,0.5472,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0125,0.9884,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9812,0.0029,0.0043,0.0001</t>
-  </si>
-  <si>
-    <t>0.9469,0.0004,0.0455,0.0008</t>
-  </si>
-  <si>
-    <t>0.9928,0.0001,0.0008,0.0010</t>
-  </si>
-  <si>
-    <t>0.7147,0.0484,0.0909,0.0087</t>
-  </si>
-  <si>
-    <t>0.8965,0.0002,0.1140,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9997,0.0003</t>
-  </si>
-  <si>
-    <t>0.0013,0.0009,0.9927,0.0024</t>
-  </si>
-  <si>
-    <t>0.0021,0.0119,0.9878,0.0015</t>
-  </si>
-  <si>
-    <t>0.0041,0.0003,0.9957,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0032,0.9914,0.0006</t>
-  </si>
-  <si>
-    <t>0.9987,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9934,0.0031,0.0008,0.0009</t>
-  </si>
-  <si>
-    <t>0.9991,0.0008,0.0001,0.0000</t>
+    <t>0.0000,0.0005,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0533,0.0018,0.9440,0.0006</t>
+  </si>
+  <si>
+    <t>0.0176,0.0006,0.9828,0.0003</t>
+  </si>
+  <si>
+    <t>0.4950,0.0477,0.3247,0.0021</t>
+  </si>
+  <si>
+    <t>0.2239,0.0141,0.7381,0.0004</t>
+  </si>
+  <si>
+    <t>0.0496,0.3694,0.3239,0.0005</t>
+  </si>
+  <si>
+    <t>0.6986,0.0015,0.4692,0.0001</t>
+  </si>
+  <si>
+    <t>0.9463,0.0052,0.0162,0.0020</t>
+  </si>
+  <si>
+    <t>0.6843,0.0163,0.1916,0.0029</t>
+  </si>
+  <si>
+    <t>0.0013,0.9981,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9993,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.5856,0.5902,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.8093,0.3226,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0042,0.9951,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.7267,0.0654,0.0786,0.0010</t>
+  </si>
+  <si>
+    <t>0.9905,0.0001,0.0037,0.0003</t>
+  </si>
+  <si>
+    <t>0.9674,0.0007,0.0025,0.0064</t>
+  </si>
+  <si>
+    <t>0.6113,0.0222,0.2505,0.0051</t>
+  </si>
+  <si>
+    <t>0.7710,0.0067,0.1351,0.0042</t>
+  </si>
+  <si>
+    <t>0.0018,0.0003,0.9972,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9981,0.0008</t>
+  </si>
+  <si>
+    <t>0.0610,0.0040,0.9101,0.0018</t>
+  </si>
+  <si>
+    <t>0.0053,0.0005,0.9922,0.0002</t>
+  </si>
+  <si>
+    <t>0.0142,0.0780,0.8454,0.0010</t>
+  </si>
+  <si>
+    <t>0.9972,0.0010,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9728,0.0309,0.0019,0.0005</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0468,0.2061,0.7482,0.0011</t>
-  </si>
-  <si>
-    <t>0.9843,0.0008,0.0067,0.0010</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0554,0.9924,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0222,0.0008,0.9745,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0020,0.0008,0.9940,0.0022</t>
-  </si>
-  <si>
-    <t>0.0007,0.0154,0.9968,0.0006</t>
-  </si>
-  <si>
-    <t>0.9579,0.0010,0.0253,0.0010</t>
-  </si>
-  <si>
-    <t>0.9429,0.0003,0.0411,0.0012</t>
-  </si>
-  <si>
-    <t>0.9955,0.0003,0.0007,0.0001</t>
+    <t>0.9969,0.0028,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0020,0.9992,0.0005</t>
+  </si>
+  <si>
+    <t>0.0158,0.0085,0.9486,0.0040</t>
+  </si>
+  <si>
+    <t>0.9584,0.0006,0.0131,0.0052</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.0818,0.9547,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0723,0.0012,0.9401,0.0006</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0001,0.9980,0.0007</t>
+  </si>
+  <si>
+    <t>0.0005,0.0015,0.9976,0.0003</t>
+  </si>
+  <si>
+    <t>0.8236,0.0019,0.1602,0.0008</t>
+  </si>
+  <si>
+    <t>0.9257,0.0007,0.0482,0.0017</t>
+  </si>
+  <si>
+    <t>0.9967,0.0001,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0026,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0005,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0002,0.0001</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9896,0.0158,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9927,0.0076,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0331,0.0213,0.8907,0.0013</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9991,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.7036,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0140,0.0148,0.9378,0.0017</t>
-  </si>
-  <si>
-    <t>0.0102,0.0001,0.9932,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9519,0.0437</t>
-  </si>
-  <si>
-    <t>0.1965,0.0003,0.8112,0.0008</t>
-  </si>
-  <si>
-    <t>0.0178,0.0005,0.9731,0.0034</t>
-  </si>
-  <si>
-    <t>0.9743,0.0000,0.0005,0.0206</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0242,0.0000,0.0000,0.9975</t>
-  </si>
-  <si>
-    <t>0.9946,0.0003,0.0001,0.0008</t>
+    <t>0.0008,0.0023,0.9960,0.0007</t>
+  </si>
+  <si>
+    <t>0.0009,0.0015,0.9977,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0563,0.9980,0.0001</t>
+  </si>
+  <si>
+    <t>0.0054,0.0106,0.9759,0.0015</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9985,0.0004</t>
+  </si>
+  <si>
+    <t>0.0075,0.0000,0.8962,0.0368</t>
+  </si>
+  <si>
+    <t>0.0105,0.0019,0.9836,0.0006</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9977,0.0008</t>
+  </si>
+  <si>
+    <t>0.9891,0.0000,0.0011,0.0050</t>
+  </si>
+  <si>
+    <t>0.0022,0.0040,0.0000,0.9987</t>
+  </si>
+  <si>
+    <t>0.0222,0.0000,0.0000,0.9964</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0001,0.0001,0.0001</t>
   </si>
 </sst>
 </file>
@@ -1857,7 +1875,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1871,7 +1889,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1885,7 +1903,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1899,7 +1917,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1913,7 +1931,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1927,7 +1945,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1941,7 +1959,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1955,7 +1973,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1983,7 +2001,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1997,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2011,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2025,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2039,7 +2057,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2053,7 +2071,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2067,7 +2085,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2081,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2095,7 +2113,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2109,7 +2127,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2123,7 +2141,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2137,7 +2155,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2151,7 +2169,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2165,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2176,10 +2194,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2193,7 +2211,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2207,7 +2225,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2221,7 +2239,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2235,7 +2253,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2249,7 +2267,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2263,7 +2281,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2277,7 +2295,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2291,7 +2309,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2305,7 +2323,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2319,7 +2337,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2333,7 +2351,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2347,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2361,7 +2379,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2375,7 +2393,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2389,7 +2407,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2403,7 +2421,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2417,7 +2435,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2431,7 +2449,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2445,7 +2463,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2459,7 +2477,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2473,7 +2491,7 @@
         <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2487,7 +2505,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2501,7 +2519,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2515,7 +2533,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2529,7 +2547,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2543,7 +2561,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2557,7 +2575,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2571,7 +2589,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2585,7 +2603,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2599,7 +2617,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2613,7 +2631,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2627,7 +2645,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>316</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2641,7 +2659,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2655,7 +2673,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2669,7 +2687,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>269</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2683,7 +2701,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2697,7 +2715,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2711,7 +2729,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2725,7 +2743,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2739,7 +2757,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2753,7 +2771,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2767,7 +2785,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2781,7 +2799,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2795,7 +2813,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2809,7 +2827,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2820,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2837,7 +2855,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2851,7 +2869,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2865,7 +2883,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2876,10 +2894,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2893,7 +2911,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2907,7 +2925,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2921,7 +2939,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2935,7 +2953,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2949,7 +2967,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2963,7 +2981,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2977,7 +2995,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2991,7 +3009,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3005,7 +3023,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3019,7 +3037,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3033,7 +3051,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3047,7 +3065,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3058,10 +3076,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3075,7 +3093,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3089,7 +3107,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3103,7 +3121,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>269</v>
+        <v>349</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3117,7 +3135,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3131,7 +3149,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3145,7 +3163,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3159,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3173,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3187,7 +3205,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3201,7 +3219,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3215,7 +3233,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3229,7 +3247,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>347</v>
+        <v>273</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3243,7 +3261,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3257,7 +3275,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3271,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3285,7 +3303,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3299,7 +3317,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3313,7 +3331,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3327,7 +3345,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3341,7 +3359,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3355,7 +3373,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3369,7 +3387,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>329</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3383,7 +3401,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3397,7 +3415,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3411,7 +3429,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3425,7 +3443,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3436,10 +3454,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3450,10 +3468,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3464,10 +3482,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3481,7 +3499,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3492,10 +3510,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3509,7 +3527,7 @@
         <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3523,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3537,7 +3555,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3551,7 +3569,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3565,7 +3583,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3579,7 +3597,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3593,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3607,7 +3625,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3621,7 +3639,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3635,7 +3653,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3649,7 +3667,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3663,7 +3681,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3677,7 +3695,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>347</v>
+        <v>271</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3691,7 +3709,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3705,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3719,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>376</v>
+        <v>271</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3730,10 +3748,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3747,7 +3765,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3761,7 +3779,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3775,7 +3793,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3789,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3800,10 +3818,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3814,10 +3832,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3831,7 +3849,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3845,7 +3863,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3859,7 +3877,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3873,7 +3891,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3887,7 +3905,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3901,7 +3919,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3915,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>352</v>
+        <v>396</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3929,7 +3947,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3943,7 +3961,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>395</v>
+        <v>271</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3957,7 +3975,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3971,7 +3989,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3985,7 +4003,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3999,7 +4017,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
+        <v>401</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4013,7 +4031,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4027,7 +4045,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4041,7 +4059,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4055,7 +4073,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4069,7 +4087,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4083,7 +4101,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4094,10 +4112,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D162" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4111,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4125,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4139,7 +4157,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4153,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>352</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4167,7 +4185,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4181,7 +4199,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4195,7 +4213,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4209,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4223,7 +4241,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4251,7 +4269,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4262,10 +4280,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4279,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4290,10 +4308,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4307,7 +4325,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4321,7 +4339,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4335,7 +4353,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4349,7 +4367,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4363,7 +4381,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4377,7 +4395,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4391,7 +4409,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4405,7 +4423,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4419,7 +4437,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4433,7 +4451,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4447,7 +4465,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4461,7 +4479,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4475,7 +4493,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4489,7 +4507,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4503,7 +4521,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4514,10 +4532,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D192" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4528,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4542,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D194" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4559,7 +4577,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4573,7 +4591,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4584,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4601,7 +4619,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4615,7 +4633,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4626,10 +4644,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4640,10 +4658,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4657,7 +4675,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4671,7 +4689,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4685,7 +4703,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4699,7 +4717,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4713,7 +4731,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4727,7 +4745,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4741,7 +4759,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4755,7 +4773,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4769,7 +4787,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4783,7 +4801,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4797,7 +4815,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4811,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4825,7 +4843,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4839,7 +4857,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4853,7 +4871,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4867,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>352</v>
+        <v>458</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4881,7 +4899,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>320</v>
+        <v>459</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4895,7 +4913,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>456</v>
+        <v>272</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4909,7 +4927,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>412</v>
+        <v>460</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4923,7 +4941,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>325</v>
+        <v>461</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4937,7 +4955,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4951,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4965,7 +4983,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4979,7 +4997,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>460</v>
+        <v>431</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4993,7 +5011,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5007,7 +5025,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5021,7 +5039,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5035,7 +5053,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5049,7 +5067,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5063,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5077,7 +5095,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5091,7 +5109,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5105,7 +5123,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5119,7 +5137,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>470</v>
+        <v>272</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5133,7 +5151,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5147,7 +5165,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5161,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5175,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>411</v>
+        <v>271</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5189,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>320</v>
+        <v>476</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5203,7 +5221,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5217,7 +5235,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5231,7 +5249,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5245,7 +5263,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5256,10 +5274,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5273,7 +5291,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5287,7 +5305,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5301,7 +5319,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5315,7 +5333,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5329,7 +5347,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5343,7 +5361,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5357,7 +5375,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5371,7 +5389,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5385,7 +5403,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>390</v>
+        <v>490</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5399,7 +5417,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5413,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
